--- a/safety_inspection_forms/015_ppe_safety_checklist--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/015_ppe_safety_checklist--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ppe_equipment_label</t>
+          <t>ppe_equipment_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ppe_equipment</t>
+          <t>What type of PPE equipment used?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,23 +538,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label</t>
+          <t>ppe_equipment_condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ppe_equipment_type</t>
+          <t>Is the PPE equipment in good condition?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_2</t>
+          <t>ppe_equipment_worn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>personal_protection_equipment</t>
+          <t>Is the PPE equipment properly worn?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_3</t>
+          <t>ppe_equipment_label</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ppe_equipment_type</t>
+          <t>What is the PPE equipment label?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,248 +612,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_4</t>
+          <t>ppe_equipment_storage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ppe_equipment_type</t>
+          <t>Is the PPE equipment properly stored?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_5</t>
+          <t>ppe_equipment_cleaning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ppe_equipment_type</t>
+          <t>Is the PPE equipment cleaned and sanitized regularly?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ppe_equipment_label_2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_8</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_9</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used_label_2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ppe_equipment_used</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,10 +661,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -896,24 +689,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_choices</t>
+          <t>ppe_equipment_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hardhat</t>
+          <t>hard_hat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hardhat</t>
+          <t>Hard Hat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_choices</t>
+          <t>ppe_equipment_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -923,14 +716,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>safety_glasses</t>
+          <t>Safety Glasses</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_choices</t>
+          <t>ppe_equipment_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -940,14 +733,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>face_shield</t>
+          <t>Face Shield</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ppe_equipment_type_label_choices</t>
+          <t>ppe_equipment_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -957,313 +750,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_3_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_3_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>safety_goggles</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>safety_goggles</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_3_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>respirator</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>respirator</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_5_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_5_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_7_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>hard_hat</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>hard_hat</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_7_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>safety_glasses</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>safety_glasses</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_7_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>face_shield</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>face_shield</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_7_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_8_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>safety_goggles</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>safety_goggles</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>respirator</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>respirator</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_10_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_10_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>safety_goggles</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>safety_goggles</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_12_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>face_shield</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>face_shield</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_12_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>safety_gloves</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_13_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>hard_hat</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>hard_hat</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ppe_equipment_type_label_13_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>earplugs</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>earplugs</t>
+          <t>Safety Gloves</t>
         </is>
       </c>
     </row>
